--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2016-11-07</t>
+          <t>2016-11-08</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -942,7 +942,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2016-10-27</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2016-11-07</t>
+          <t>2016-11-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2016-12-08</t>
+          <t>2016-12-09</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2017-01-17</t>
+          <t>2017-01-18</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2017-02-22</t>
+          <t>2017-02-23</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2016-11-07</t>
+          <t>2016-11-08</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2016-12-13</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2016-11-13</t>
+          <t>2016-11-14</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2017-01-17</t>
+          <t>2017-01-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2017-03-19</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-08-02</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2019-09-12</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2621,7 +2621,7 @@
           <t>- | 4493呎 (4+房)
 $91200万
 $202,982/呎
-(16年-11月-07日)</t>
+(16年-11月-08日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
           <t>- | 4538呎 (4+房)
 $68578万
 $151,119/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
           <t>- | 4548呎 (4+房)
 $74902万
 $164,692/呎
-(16年-10月-27日)</t>
+(16年-10月-28日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
           <t>- | 4566呎 (4+房)
 $65200万
 $142,795/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
           <t>- | 4566呎 (4+房)
 $64464万
 $141,184/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
           <t>- | 4566呎 (4+房)
 $64642万
 $141,571/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
           <t>- | 4566呎 (4+房)
 $35039万
 $76,739/呎
-(16年-11月-07日)</t>
+(16年-11月-08日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
           <t>- | 4566呎 (4+房)
 $31200万
 $68,331/呎
-(16年-12月-08日)</t>
+(16年-12月-09日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
           <t>- | 4566呎 (4+房)
 $59328万
 $129,935/呎
-(17年-01月-17日)</t>
+(17年-01月-18日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
           <t>- | 4566呎 (4+房)
 $30820万
 $67,500/呎
-(17年-02月-22日)</t>
+(17年-02月-23日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
           <t>- | 4569呎 (4+房)
 $56800万
 $124,316/呎
-(17年-03月-19日)</t>
+(17年-03月-20日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
           <t>- | 4209呎 (4+房)
 $91200万
 $216,679/呎
-(16年-11月-07日)</t>
+(16年-11月-08日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2940,7 +2940,7 @@
           <t>- | 4254呎 (4+房)
 $68578万
 $161,207/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
           <t>- | 4264呎 (4+房)
 $38000万
 $89,118/呎
-(20年-04月-28日)</t>
+(20年-04月-29日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
           <t>- | 4289呎 (4+房)
 $65200万
 $152,017/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
           <t>- | 4289呎 (4+房)
 $64464万
 $150,302/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
           <t>- | 4289呎 (4+房)
 $64642万
 $150,715/呎
-(16年-10月-19日)</t>
+(16年-10月-20日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
           <t>- | 4289呎 (4+房)
 $31653万
 $73,800/呎
-(16年-12月-13日)</t>
+(16年-12月-14日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
           <t>- | 4289呎 (4+房)
 $27278万
 $63,600/呎
-(16年-11月-13日)</t>
+(16年-11月-14日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
           <t>- | 4289呎 (4+房)
 $59328万
 $138,327/呎
-(17年-01月-17日)</t>
+(17年-01月-18日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
           <t>- | 4289呎 (4+房)
 $28736万
 $66,999/呎
-(17年-07月-13日)</t>
+(17年-07月-14日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
           <t>- | 4281呎 (4+房)
 $56800万
 $132,679/呎
-(17年-03月-19日)</t>
+(17年-03月-20日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
           <t>B | 4217呎 (4+房)
 $60900万
 $144,415/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         <is>
           <t>21号屋
 6326呎 (3房)
-(19年-08月-01日)
+(19年-08月-02日)
 $5.39亿
 $85,188/呎</t>
         </is>
@@ -3235,7 +3235,7 @@
         <is>
           <t>22号屋
 7008呎 (4+房)
-(19年-09月-12日)
+(19年-09月-13日)
 $5.81亿
 $82,889/呎</t>
         </is>

--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2514,23 +2514,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>A座 销控网格图</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mount Nicholson II - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -2561,250 +2561,83 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>- | 4493呎 (4+房)
-$91200万
-$202,982/呎
-(16年-11月-08日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>21号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>- | 4538呎 (4+房)
-$68578万
-$151,119/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>- | 4548呎 (4+房)
-$74902万
-$164,692/呎
-(16年-10月-28日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$65200万
-$142,795/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$64464万
-$141,184/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$64642万
-$141,571/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$35039万
-$76,739/呎
-(16年-11月-08日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$31200万
-$68,331/呎
-(16年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$59328万
-$129,935/呎
-(17年-01月-18日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$30820万
-$67,500/呎
-(17年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>- | 4569呎 (4+房)
-$56800万
-$124,316/呎
-(17年-03月-20日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr"/>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>A | 4499呎 (4+房)
--
--
-(待售)</t>
+          <t>21号屋
+6326呎 (3房)
+(19年-08月-02日)
+$5.39亿
+$85,188/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>22号屋
+7008呎 (4+房)
+(19年-09月-13日)
+$5.81亿
+$82,889/呎</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2828,7 +2661,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>B座 销控网格图</t>
+          <t>A座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2715,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -2892,7 +2725,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2742,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2921,9 +2754,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>- | 4209呎 (4+房)
+          <t>- | 4493呎 (4+房)
 $91200万
-$216,679/呎
+$202,982/呎
 (16年-11月-08日)</t>
         </is>
       </c>
@@ -2937,9 +2770,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>- | 4254呎 (4+房)
+          <t>- | 4538呎 (4+房)
 $68578万
-$161,207/呎
+$151,119/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -2953,10 +2786,10 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>- | 4264呎 (4+房)
-$38000万
-$89,118/呎
-(20年-04月-29日)</t>
+          <t>- | 4548呎 (4+房)
+$74902万
+$164,692/呎
+(16年-10月-28日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2969,9 +2802,9 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
+          <t>- | 4566呎 (4+房)
 $65200万
-$152,017/呎
+$142,795/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -2985,9 +2818,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
+          <t>- | 4566呎 (4+房)
 $64464万
-$150,302/呎
+$141,184/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -3001,9 +2834,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
+          <t>- | 4566呎 (4+房)
 $64642万
-$150,715/呎
+$141,571/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -3017,10 +2850,10 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
-$31653万
-$73,800/呎
-(16年-12月-14日)</t>
+          <t>- | 4566呎 (4+房)
+$35039万
+$76,739/呎
+(16年-11月-08日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -3033,10 +2866,10 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
-$27278万
-$63,600/呎
-(16年-11月-14日)</t>
+          <t>- | 4566呎 (4+房)
+$31200万
+$68,331/呎
+(16年-12月-09日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -3049,9 +2882,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
+          <t>- | 4566呎 (4+房)
 $59328万
-$138,327/呎
+$129,935/呎
 (17年-01月-18日)</t>
         </is>
       </c>
@@ -3065,10 +2898,10 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>- | 4289呎 (4+房)
-$28736万
-$66,999/呎
-(17年-07月-14日)</t>
+          <t>- | 4566呎 (4+房)
+$30820万
+$67,500/呎
+(17年-02月-23日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -3081,9 +2914,9 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>- | 4281呎 (4+房)
+          <t>- | 4569呎 (4+房)
 $56800万
-$132,679/呎
+$124,316/呎
 (17年-03月-20日)</t>
         </is>
       </c>
@@ -3096,12 +2929,12 @@
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 4217呎 (4+房)
-$60900万
-$144,415/呎
-(25年-06月-09日)</t>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>A | 4499呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -3120,23 +2953,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Nicholson II - 独立屋销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -3167,83 +3000,250 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21号屋</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>22号屋</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>- | 4209呎 (4+房)
+$91200万
+$216,679/呎
+(16年-11月-08日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>21号屋
-6326呎 (3房)
-(19年-08月-02日)
-$5.39亿
-$85,188/呎</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>22号屋
-7008呎 (4+房)
-(19年-09月-13日)
-$5.81亿
-$82,889/呎</t>
+          <t>- | 4254呎 (4+房)
+$68578万
+$161,207/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>- | 4264呎 (4+房)
+$38000万
+$89,118/呎
+(20年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$65200万
+$152,017/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$64464万
+$150,302/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$64642万
+$150,715/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$31653万
+$73,800/呎
+(16年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$27278万
+$63,600/呎
+(16年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$59328万
+$138,327/呎
+(17年-01月-18日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$28736万
+$66,999/呎
+(17年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>- | 4281呎 (4+房)
+$56800万
+$132,679/呎
+(17年-03月-20日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 4217呎 (4+房)
+$60900万
+$144,415/呎
+(25年-06月-09日)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2514,23 +2514,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Nicholson II - 独立屋销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -2561,83 +2561,250 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21号屋</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>22号屋</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>- | 4493呎 (4+房)
+$91200万
+$202,982/呎
+(16年-11月-08日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>21号屋
-6326呎 (3房)
-(19年-08月-02日)
-$5.39亿
-$85,188/呎</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>22号屋
-7008呎 (4+房)
-(19年-09月-13日)
-$5.81亿
-$82,889/呎</t>
+          <t>- | 4538呎 (4+房)
+$68578万
+$151,119/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>- | 4548呎 (4+房)
+$74902万
+$164,692/呎
+(16年-10月-28日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$65200万
+$142,795/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$64464万
+$141,184/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$64642万
+$141,571/呎
+(16年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$35039万
+$76,739/呎
+(16年-11月-08日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$31200万
+$68,331/呎
+(16年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$59328万
+$129,935/呎
+(17年-01月-18日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$30820万
+$67,500/呎
+(17年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>- | 4569呎 (4+房)
+$56800万
+$124,316/呎
+(17年-03月-20日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>A | 4499呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2661,7 +2828,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A座 销控网格图</t>
+          <t>B座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2882,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -2725,7 +2892,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2909,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2754,9 +2921,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>- | 4493呎 (4+房)
+          <t>- | 4209呎 (4+房)
 $91200万
-$202,982/呎
+$216,679/呎
 (16年-11月-08日)</t>
         </is>
       </c>
@@ -2770,9 +2937,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>- | 4538呎 (4+房)
+          <t>- | 4254呎 (4+房)
 $68578万
-$151,119/呎
+$161,207/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -2786,10 +2953,10 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>- | 4548呎 (4+房)
-$74902万
-$164,692/呎
-(16年-10月-28日)</t>
+          <t>- | 4264呎 (4+房)
+$38000万
+$89,118/呎
+(20年-04月-29日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2802,9 +2969,9 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
+          <t>- | 4289呎 (4+房)
 $65200万
-$142,795/呎
+$152,017/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -2818,9 +2985,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
+          <t>- | 4289呎 (4+房)
 $64464万
-$141,184/呎
+$150,302/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -2834,9 +3001,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
+          <t>- | 4289呎 (4+房)
 $64642万
-$141,571/呎
+$150,715/呎
 (16年-10月-20日)</t>
         </is>
       </c>
@@ -2850,10 +3017,10 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
-$35039万
-$76,739/呎
-(16年-11月-08日)</t>
+          <t>- | 4289呎 (4+房)
+$31653万
+$73,800/呎
+(16年-12月-14日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -2866,10 +3033,10 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
-$31200万
-$68,331/呎
-(16年-12月-09日)</t>
+          <t>- | 4289呎 (4+房)
+$27278万
+$63,600/呎
+(16年-11月-14日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2882,9 +3049,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
+          <t>- | 4289呎 (4+房)
 $59328万
-$129,935/呎
+$138,327/呎
 (17年-01月-18日)</t>
         </is>
       </c>
@@ -2898,10 +3065,10 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>- | 4566呎 (4+房)
-$30820万
-$67,500/呎
-(17年-02月-23日)</t>
+          <t>- | 4289呎 (4+房)
+$28736万
+$66,999/呎
+(17年-07月-14日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2914,9 +3081,9 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>- | 4569呎 (4+房)
+          <t>- | 4281呎 (4+房)
 $56800万
-$124,316/呎
+$132,679/呎
 (17年-03月-20日)</t>
         </is>
       </c>
@@ -2929,12 +3096,12 @@
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr"/>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>A | 4499呎 (4+房)
--
--
-(待售)</t>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 4217呎 (4+房)
+$60900万
+$144,415/呎
+(25年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -2953,23 +3120,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>B座 销控网格图</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mount Nicholson II - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -3000,250 +3167,83 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>- | 4209呎 (4+房)
-$91200万
-$216,679/呎
-(16年-11月-08日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>21号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>- | 4254呎 (4+房)
-$68578万
-$161,207/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>- | 4264呎 (4+房)
-$38000万
-$89,118/呎
-(20年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$65200万
-$152,017/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$64464万
-$150,302/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$64642万
-$150,715/呎
-(16年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$31653万
-$73,800/呎
-(16年-12月-14日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$27278万
-$63,600/呎
-(16年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$59328万
-$138,327/呎
-(17年-01月-18日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$28736万
-$66,999/呎
-(17年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>- | 4281呎 (4+房)
-$56800万
-$132,679/呎
-(17年-03月-20日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 4217呎 (4+房)
-$60900万
-$144,415/呎
-(25年-06月-09日)</t>
+          <t>21号屋
+6326呎 (3房)
+(19年-08月-02日)
+$5.39亿
+$85,188/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>22号屋
+7008呎 (4+房)
+(19年-09月-13日)
+$5.81亿
+$82,889/呎</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
